--- a/Monthly Payout/Golden_Panda_Pay_2026-07.xlsx
+++ b/Monthly Payout/Golden_Panda_Pay_2026-07.xlsx
@@ -1,47 +1,217 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2aab30d5f179594d/Desktop/Golden Panda Staffing/Monthly Payout/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_3FCA950F115746007C300762746830B55D94A3B6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9660F38E-8383-42F6-B123-7E5F2A7B45AC}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Monthly Pay" sheetId="1" r:id="rId1"/>
+    <sheet name="Working Details" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="55">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>IC Number</t>
+  </si>
+  <si>
+    <t>Bank Name</t>
+  </si>
+  <si>
+    <t>Bank Account</t>
+  </si>
+  <si>
+    <t>Roadshow Days</t>
+  </si>
+  <si>
+    <t>Total Pay (RM)</t>
+  </si>
+  <si>
+    <t>Total Commission (RM)</t>
+  </si>
+  <si>
+    <t>Total Payout (RM)</t>
+  </si>
+  <si>
+    <t>Choy Yew Wei</t>
+  </si>
+  <si>
+    <t>050321-14-1185</t>
+  </si>
+  <si>
+    <t>Public Bank</t>
+  </si>
+  <si>
+    <t>5060 0981 10</t>
+  </si>
+  <si>
+    <t>Tho Sweet Ning</t>
+  </si>
+  <si>
+    <t>050306-08-1022</t>
+  </si>
+  <si>
+    <t>5009041225</t>
+  </si>
+  <si>
+    <t>Liew Yu Heng</t>
+  </si>
+  <si>
+    <t>050913-14-0215</t>
+  </si>
+  <si>
+    <t>Maybank</t>
+  </si>
+  <si>
+    <t>1622 4583 6082</t>
+  </si>
+  <si>
+    <t>Hua Wei Sheng</t>
+  </si>
+  <si>
+    <t>050409-14-0945</t>
+  </si>
+  <si>
+    <t>156244229062</t>
+  </si>
+  <si>
+    <t>Ong Huai Zhou</t>
+  </si>
+  <si>
+    <t>050204-07-0605</t>
+  </si>
+  <si>
+    <t>Hong Leong Bank</t>
+  </si>
+  <si>
+    <t>3225 0194 537</t>
+  </si>
+  <si>
+    <t>Angel Ooi Kai Xin</t>
+  </si>
+  <si>
+    <t>081028-10-1960</t>
+  </si>
+  <si>
+    <t>1641 1921 9968</t>
+  </si>
+  <si>
+    <t>Chew Sin Yen</t>
+  </si>
+  <si>
+    <t>050424-02-0458</t>
+  </si>
+  <si>
+    <t>3955 0450 424</t>
+  </si>
+  <si>
+    <t>Tham Yee Ting</t>
+  </si>
+  <si>
+    <t>050707-14-1292</t>
+  </si>
+  <si>
+    <t>5096993032</t>
+  </si>
+  <si>
+    <t>Crew Name</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Hours Worked</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>de Market</t>
+  </si>
+  <si>
+    <t>Promoter</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Assistant</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>PG Mall</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Mascot</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,14 +234,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,57 +577,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>IC Number</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bank Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Bank Account</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Roadshow Days</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Total Pay (RM)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Total Commission (RM)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Total Payout (RM)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Choy Yew Wei</v>
-      </c>
-      <c r="B2" t="str">
-        <v>050321-14-1185</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Public Bank</v>
-      </c>
-      <c r="D2" t="str">
-        <v>5060 0981 10</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -461,18 +641,18 @@
         <v>530</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Victoria</v>
-      </c>
-      <c r="B3" t="str">
-        <v>050306-08-1022</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Public Bank</v>
-      </c>
-      <c r="D3" t="str">
-        <v>5009041225</v>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -487,18 +667,18 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Liew Yu Heng</v>
-      </c>
-      <c r="B4" t="str">
-        <v>050913-14-0215</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Maybank</v>
-      </c>
-      <c r="D4" t="str">
-        <v>1622 4583 6082</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -513,18 +693,18 @@
         <v>470</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Hua Wei Sheng</v>
-      </c>
-      <c r="B5" t="str">
-        <v>050409-14-0945</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Maybank</v>
-      </c>
-      <c r="D5" t="str">
-        <v>156244229062</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -539,18 +719,18 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Ong Huai Zhou</v>
-      </c>
-      <c r="B6" t="str">
-        <v>050204-07-0605</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Hong Leong Bank</v>
-      </c>
-      <c r="D6" t="str">
-        <v>3225 0194 537</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -565,18 +745,18 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Angel Ooi Kai Xin</v>
-      </c>
-      <c r="B7" t="str">
-        <v>081028-10-1960</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Maybank</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1641 1921 9968</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -591,18 +771,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Tham Yee Ting</v>
-      </c>
-      <c r="B8" t="str">
-        <v>050707-14-1292</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Public Bank</v>
-      </c>
-      <c r="D8" t="str">
-        <v>5096993032</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -617,18 +797,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Chew Sin Yen</v>
-      </c>
-      <c r="B9" t="str">
-        <v>050424-02-0458</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Hong Leong Bank</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3955 0450 424</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -644,8 +824,633 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError sqref="A1:H9" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46222.000289351854</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46229.000289351854</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46214.000289351854</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46221.000289351854</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46222.000289351854</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46228.000289351854</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46229.000289351854</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46214.000289351854</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46215.000289351854</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46215.000289351854</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46221.000289351854</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46222.000289351854</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46228.000289351854</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46229.000289351854</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46214.000289351854</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46215.000289351854</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46214.000289351854</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46214.000289351854</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46215.000289351854</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46221.000289351854</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46222.000289351854</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46229.000289351854</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H23" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>